--- a/Weekly_Payments_List_ Aug 2026.xlsx
+++ b/Weekly_Payments_List_ Aug 2026.xlsx
@@ -5,17 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_Aug_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B5930E7-ABAB-40F3-8958-AEA61B2CC4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8689DDB5-763B-4E09-BFA3-5265C1A9AA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B02E05AF-7D43-4983-B01B-A94CFD3A6612}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{B02E05AF-7D43-4983-B01B-A94CFD3A6612}"/>
   </bookViews>
   <sheets>
     <sheet name="Date_08-08-2026 to 14 - 08-2026" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Date_15-08-2026 to 21 - 08-2026" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Date_08-08-2026 to 14 - 08-2026'!$A$3:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Date_15-08-2026 to 21 - 08-2026'!$A$3:$F$3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>M/S KRISHI INFRATECH,SOMPETA</t>
   </si>
@@ -68,13 +72,49 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>17-08-2026</t>
+  </si>
+  <si>
+    <t>Total payment ₹96,570; Paid ₹50,000; Balance ₹46,570</t>
+  </si>
+  <si>
+    <t>20-08-2026</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Murali Technical Works – Installed 10 No's cameras for camp office.</t>
+  </si>
+  <si>
+    <t>CNT/26-27/16</t>
+  </si>
+  <si>
+    <t>G_14</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sri Sai Chinthamani Traders – 25mm 11 No's    L-angles for press racks   &amp;    10mm 14 No's            L-angles for store. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Total 333.2 kg × 68.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,6 +149,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -136,7 +183,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -183,11 +230,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -220,6 +282,31 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -574,10 +661,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
+      </c>
+      <c r="B4" s="4">
+        <v>46273</v>
       </c>
       <c r="C4" s="3">
         <v>12</v>
@@ -589,9 +676,9 @@
         <v>4650</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>7</v>
@@ -626,15 +713,125 @@
       <c r="E7" s="11"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:E3" xr:uid="{D2DD5440-15A1-40D8-82EA-C50F3BBF0598}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3204AF87-B37C-411D-B04E-511F3EA3C885}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="41.42578125" customWidth="1"/>
+    <col min="5" max="5" width="37.140625" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>28</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="14">
+        <v>46570</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
+        <v>29</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="14">
+        <v>22590</v>
+      </c>
+      <c r="F5" s="16"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="20">
+        <f>SUM(E4:E5)</f>
+        <v>69160</v>
+      </c>
+      <c r="F6" s="16"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="16"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F3" xr:uid="{3204AF87-B37C-411D-B04E-511F3EA3C885}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>